--- a/Paket_1_Matematika_TKA_SD.xlsx
+++ b/Paket_1_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 1 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Sebuah toko alat tulis memiliki persediaan 24 kotak pensil. Setiap kotak berisi 12 batang pensil. Toko tersebut mendapatkan kiriman tambahan sebanyak 75 batang pensil. Jika pada hari itu terjual 148 batang pensil, berapakah sisa pensil di toko tersebut sekarang?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  215 batang</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  225 batang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  235 batang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  245 batang</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Suhu di dalam ruang pendingin daging mula-mula adalah -8°C. Karena terjadi pemadaman listrik, suhu di dalam ruang pendingin naik 3°C setiap 15 menit. Berapakah suhu di dalam ruang pendingin tersebut setelah listrik padam selama 1 jam?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  -4°C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  4°C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  -2°C</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  2°C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Ibu Ratna membeli 3 1/2 kg tepung terigu. Sebanyak 1 3/4 kg digunakan untuk membuat kue bolu dan 0,5 kg digunakan untuk membuat bakwan. Berapa kilogram sisa tepung terigu Ibu Ratna sekarang?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  1 1/4 kg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  1 1/2 kg</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  1 3/4 kg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  2 1/4 kg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Perbandingan banyak siswa laki-laki dan perempuan di kelas 6 SD Harapan Bangsa adalah 3 : 5. Jika jumlah seluruh siswa di kelas tersebut adalah 40 orang, selisih banyak siswa perempuan dan laki-laki adalah....</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  8 orang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  10 orang</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  12 orang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  15 orang</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,37 +637,42 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Pak Ahmad memanen 48 buah mangga dan 72 buah jeruk. Buah-buah tersebut akan dimasukkan ke dalam beberapa keranjang dengan jumlah mangga dan jeruk sama banyak pada setiap keranjang tanpa ada buah yang tersisa.
+Manakah pernyataan berikut yang bernilai BENAR? (Pilihlah lebih dari satu jawaban!)  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Jumlah keranjang terbanyak yang dapat disiapkan Pak Ahmad adalah 24 buah.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Setiap keranjang akan berisi 2 buah mangga.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Setiap keranjang akan berisi 4 buah jeruk.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Total buah di dalam setiap keranjang adalah 5 buah.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,7 +683,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +697,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Sebuah taman bunga berbentuk persegi memiliki luas 625 m². Di sekeliling taman tersebut akan dipasang pagar pembatas kawat. Panjang kawat minimal yang dibutuhkan untuk memagari taman tersebut satu putaran penuh adalah....</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  50 meter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  75 meter</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  100 meter</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  125 meter</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,17 +728,25 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Toko Buku Pintar memberikan promosi potongan harga (diskon) menjelang tahun ajaran baru. Perhatikan informasi harga dan potongan harga berikut:
+• Buku A: Harga Rp50.000 dengan diskon 20%
+• Buku B: Harga Rp40.000 dengan diskon 1/4 bagian dari harga awal
+• Buku C: Harga Rp60.000 dengan harga akhir setelah diskon menjadi Rp45.000
+Tentukan nilai kebenaran dari setiap pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,7 +777,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +791,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Rian berlatih renang setiap 4 hari sekali, Danu setiap 6 hari sekali, dan Fandi setiap 8 hari sekali di kolam renang yang sama. Jika pada hari Sabtu, 2 Mei mereka berlatih bersama untuk pertama kalinya, pada hari dan tanggal berapakah mereka akan berlatih bersama untuk kedua kalinya?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Selasa, 26 Mei</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Rabu, 27 Mei</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Selasa, 24 Mei</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Rabu, 26 Mei</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +822,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +836,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Jarak antara Kota Surabaya dan Kota Malang pada peta berskala 1 : 1.500.000 adalah 6 cm. Pak Budi mengendarai mobil dari Surabaya menuju Malang dengan kecepatan rata-rata 60 km/jam. Jika Pak Budi berangkat pukul 07.30 WIB, pukul berapakah Pak Budi tiba di Kota Malang?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  08.45 WIB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  09.00 WIB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  09.15 WIB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  09.30 WIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +867,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +881,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Sebuah truk mengangkut 1,5 ton beras, 4,5 kuintal jagung, dan 180 kg kedelai. Berapakah total berat seluruh muatan truk tersebut dalam satuan kilogram?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  2.130 kg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  2.050 kg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  1.980 kg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  2.230 kg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +912,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +926,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebuah kolam ikan memiliki volume air 1.800 liter. Kolam tersebut diisi air menggunakan pipa dengan debit 40 liter/menit. Berapakah waktu yang diperlukan agar kolam ikan tersebut terisi penuh dari keadaan kosong?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  35 menit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  45 menit</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  50 menit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  1 jam 15 menit</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,37 +957,45 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bangun datar segi empat memiliki ciri-ciri sebagai berikut:
+• Mempunyai dua pasang sisi sejajar dan sama panjang.
+• Sudut-sudut yang berhadapan sama besar (bukan sudut siku-siku).
+• Kedua diagonalnya saling membagi dua sama panjang tetapi tidak saling tegak lurus.
+Manakah pernyataan berikut yang sesuai dengan bangun datar tersebut?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Bangun datar tersebut adalah jajar genjang.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Bangun datar tersebut memiliki 2 simetri lipat.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Bangun datar tersebut memiliki simetri putar tingkat dua.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Rumus luas bangun datar tersebut adalah alas dikalikan tinggi.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,7 +1006,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1020,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebuah lapangan olahraga berbentuk persegi panjang berukuran panjang 28 meter dan lebar 14 meter. Pada kedua sisi lebar lapangan tersebut dibuat taman berbentuk setengah lingkaran dengan diameter tepat sama dengan lebar lapangan. Berapakah luas seluruh lapangan beserta kedua taman setengah lingkaran tersebut? (Gunakan π = 22/7)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  496 m²</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  546 m²</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  616 m²</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  700 m²</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1051,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1065,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah wadah air berbentuk balok memiliki ukuran panjang 80 cm, lebar 50 cm, dan tinggi 60 cm. Wadah tersebut telah terisi air sebanyak 3/4 bagian dari kapasitas totalnya. Berapa liter air yang masih harus ditambahkan agar wadah tersebut terisi penuh?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  60 liter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  80 liter</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  180 liter</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  240 liter</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1096,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Doni memiliki beberapa jaring-jaring bangun ruang yang terdiri atas bangun-bangun datar penyusunnya. Tentukan nilai kebenaran dari pernyataan terkait bentuk jaring-jaring bangun ruang berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1141,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1155,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Berikut adalah data hasil penjualan beras di Toko Makmur selama 5 hari berturut-turut:
+• Senin: 45 kg
+• Selasa: 60 kg
+• Rabu: 50 kg
+• Kamis: 75 kg
+• Jumat: 70 kg
+Berapakah rata-rata (mean) penjualan beras per hari di toko tersebut?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  58 kg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  60 kg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  62 kg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  65 kg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1192,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1206,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Data nilai ulangan matematika dari 11 siswa kelas 6 adalah sebagai berikut:
+75, 80, 85, 70, 90, 80, 85, 80, 95, 75, 85.
+Nilai median dan modus dari data nilai ulangan tersebut berturut-turut adalah....</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Median = 80 dan Modus = 80</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Median = 80 dan Modus = 80 dan 85</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Median = 85 dan Modus = 80</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Median = 85 dan Modus = 85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1239,45 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Perpustakaan SD Ceria menyajikan data pengunjung mingguan menggunakan diagram gambar (piktogram). Keterangan piktogram:
+• 1 simbol buku besar mewakili 20 pengunjung.
+• 1 simbol buku kecil mewakili 10 pengunjung.
+Pada hari Senin tercatat 3 buku besar dan 1 buku kecil. Pada hari Selasa tercatat 4 buku besar. Pada hari Rabu tercatat 2 buku besar dan 1 buku kecil.
+Manakah kesimpulan berikut yang TEPAT?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Banyak pengunjung pada hari Senin adalah 70 orang.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Banyak pengunjung pada hari Selasa adalah 80 orang.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Selisih pengunjung hari Selasa dan Rabu adalah 30 orang.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Total pengunjung selama tiga hari tersebut adalah 210 orang.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1288,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1302,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Sebuah diagram lingkaran menyajikan data hobi dari 120 siswa kelas 6 SD:
+• Sepak Bola: 40%
+• Bulu Tangkis: 25%
+• Renang: 20%
+• Sisanya hobi Melukis
+Banyak siswa yang memiliki hobi melukis adalah....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  15 orang</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  18 orang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  20 orang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  24 orang</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1338,24 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 1] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan barisan bilangan teratur berikut:
+Barisan A: 4, 9, 14, 19, 24, 29, ...
+Barisan B: 3, 6, 12, 24, 48, ...
+Tentukan nilai kebenaran dari pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1386,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
